--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124708562</v>
+        <v>124708286</v>
       </c>
       <c r="B2" t="n">
         <v>96983</v>
@@ -746,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Yta på 10 gånger tio meter</t>
+          <t>15 gånger 30 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124708286</v>
+        <v>124707981</v>
       </c>
       <c r="B2" t="n">
         <v>96983</v>
@@ -746,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>15 gånger 30 meter</t>
+          <t>På en yta av 25 gånger 25 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124707981</v>
+        <v>124708562</v>
       </c>
       <c r="B2" t="n">
         <v>96983</v>
@@ -746,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en yta av 25 gånger 25 meter</t>
+          <t>Yta på 10 gånger tio meter</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124708562</v>
+        <v>124708286</v>
       </c>
       <c r="B2" t="n">
-        <v>96983</v>
+        <v>97151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Yta på 10 gånger tio meter</t>
+          <t>15 gånger 30 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,647 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126213449</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nordvallstjärn , Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>490851</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6950066</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126208772</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stortjärnbäcken, Stortjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>490891</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6950055</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126213296</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105350</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nordvallstjärn , Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>490981</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6949788</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126213340</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nordvallstjärn , Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>490980</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6949803</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126207729</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97219</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stortjärnbäcken, Stortjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>490748</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6950177</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126213489</v>
+      </c>
+      <c r="B8" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nordvallstjärn , Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>490769</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6950140</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>126213296</v>
       </c>
       <c r="B5" t="n">
-        <v>105350</v>
+        <v>105352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>126213340</v>
       </c>
       <c r="B6" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>126207729</v>
       </c>
       <c r="B7" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>126213296</v>
       </c>
       <c r="B5" t="n">
-        <v>105352</v>
+        <v>105356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>126213340</v>
       </c>
       <c r="B6" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>126207729</v>
       </c>
       <c r="B7" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>126213449</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126208772</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126213296</v>
       </c>
       <c r="B5" t="n">
-        <v>105356</v>
+        <v>105369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>126213340</v>
       </c>
       <c r="B6" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>126207729</v>
       </c>
       <c r="B7" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>126213489</v>
       </c>
       <c r="B8" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>126213296</v>
       </c>
       <c r="B5" t="n">
-        <v>105369</v>
+        <v>105372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>126213340</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>126207729</v>
       </c>
       <c r="B7" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>126213449</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126208772</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126213296</v>
       </c>
       <c r="B5" t="n">
-        <v>105372</v>
+        <v>105381</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>126213340</v>
       </c>
       <c r="B6" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>126207729</v>
       </c>
       <c r="B7" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>126213489</v>
       </c>
       <c r="B8" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1427,6 +1427,411 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126561775</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98382</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stortjärnen , Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>490985</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6949808</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126561766</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stortjärnen , Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>490970</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6949901</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126561744</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>490857</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6950073</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126561709</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>490792</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6950118</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>126561775</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126561766</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>126561744</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>126561709</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>126561775</v>
       </c>
       <c r="B9" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126561766</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>126561744</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>126561709</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56364-2024 artfynd.xlsx
+++ b/artfynd/A 56364-2024 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>126561775</v>
       </c>
       <c r="B9" t="n">
-        <v>98463</v>
+        <v>98457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126561766</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>126561744</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>126561709</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
